--- a/jm-test/Test_cases_MiniMe.xlsx
+++ b/jm-test/Test_cases_MiniMe.xlsx
@@ -202,9 +202,6 @@
     <t>Multiple files upload (mixed types)</t>
   </si>
   <si>
-    <t>All files optimized, correct indicators shown per file</t>
-  </si>
-  <si>
     <t>Background image after optimization (image upload)</t>
   </si>
   <si>
@@ -378,12 +375,6 @@
 2. Drag and drop a large video file (&gt;500MB).
 3. Observe optimization progress.
 4. Verify numeric elapsed time and space saved are displayed.</t>
-  </si>
-  <si>
-    <t>1. Launch the application in Minime Mode.
-2. Drag and drop multiple files (images + videos).
-3. Observe optimization progress.
-4. Verify all files are optimized and indicators shown per file.</t>
   </si>
   <si>
     <t>1. Launch the application in Minime Mode.
@@ -765,9 +756,6 @@
     <t>Dropping the corrupted image produced no visible UI change and no optimization was started.</t>
   </si>
   <si>
-    <t>All selected image and video files were processed, with the corresponding completion indicators displayed for each file.</t>
-  </si>
-  <si>
     <t>After image optimization completed, the last optimized image was displayed in the application background.</t>
   </si>
   <si>
@@ -924,13 +912,25 @@
   <si>
     <t>The file was accepted and processed successfully, the application 
 remained responsive and the filename was handled correctly.</t>
+  </si>
+  <si>
+    <t>1. Launch the application in Minime Mode.
+2. Drag and drop multiple files (images + videos).
+3. Observe optimization progress.
+4. Verify all files are optimized and indicators shown.</t>
+  </si>
+  <si>
+    <t>All files optimized, correct indicators shown</t>
+  </si>
+  <si>
+    <t>All selected image and video files were processed, with the corresponding completion indicator displayed.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -948,13 +948,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1190,7 +1183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1253,26 +1246,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1292,41 +1279,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1652,7 +1639,7 @@
       <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="22" t="s">
@@ -1667,22 +1654,22 @@
         <v>8</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="28" t="s">
-        <v>181</v>
+      <c r="F2" s="41" t="s">
+        <v>179</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="45">
@@ -1693,22 +1680,22 @@
         <v>12</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="26" t="s">
-        <v>182</v>
+      <c r="F3" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G3" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60">
@@ -1716,25 +1703,25 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>183</v>
+      <c r="F4" s="8" t="s">
+        <v>181</v>
       </c>
       <c r="G4" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="75">
@@ -1742,25 +1729,25 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>184</v>
+      <c r="F5" s="8" t="s">
+        <v>182</v>
       </c>
       <c r="G5" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60">
@@ -1771,22 +1758,22 @@
         <v>17</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>185</v>
+      <c r="F6" s="8" t="s">
+        <v>183</v>
       </c>
       <c r="G6" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="75">
@@ -1794,25 +1781,25 @@
         <v>18</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>186</v>
+        <v>68</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>184</v>
       </c>
       <c r="G7" s="19" t="s">
         <v>19</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60">
@@ -1823,22 +1810,22 @@
         <v>37</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>187</v>
+      <c r="F8" s="8" t="s">
+        <v>185</v>
       </c>
       <c r="G8" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60">
@@ -1849,22 +1836,22 @@
         <v>38</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>188</v>
+      <c r="F9" s="8" t="s">
+        <v>186</v>
       </c>
       <c r="G9" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60">
@@ -1872,25 +1859,25 @@
         <v>26</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>189</v>
+      <c r="F10" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="G10" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="75">
@@ -1901,22 +1888,22 @@
         <v>40</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>190</v>
+      <c r="F11" s="8" t="s">
+        <v>188</v>
       </c>
       <c r="G11" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="60">
@@ -1927,22 +1914,22 @@
         <v>41</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="26" t="s">
-        <v>191</v>
+      <c r="F12" s="8" t="s">
+        <v>189</v>
       </c>
       <c r="G12" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60">
@@ -1953,22 +1940,22 @@
         <v>42</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="26" t="s">
-        <v>192</v>
+      <c r="F13" s="8" t="s">
+        <v>190</v>
       </c>
       <c r="G13" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="60">
@@ -1979,22 +1966,22 @@
         <v>43</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>193</v>
+        <v>97</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>191</v>
       </c>
       <c r="G14" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60">
@@ -2005,22 +1992,22 @@
         <v>28</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="26" t="s">
-        <v>194</v>
+      <c r="F15" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="G15" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="60">
@@ -2028,25 +2015,25 @@
         <v>47</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="26" t="s">
-        <v>195</v>
+      <c r="F16" s="8" t="s">
+        <v>193</v>
       </c>
       <c r="G16" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="60">
@@ -2054,25 +2041,25 @@
         <v>48</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="26" t="s">
-        <v>196</v>
+      <c r="F17" s="8" t="s">
+        <v>194</v>
       </c>
       <c r="G17" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="60">
@@ -2083,22 +2070,22 @@
         <v>46</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>197</v>
+        <v>97</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>195</v>
       </c>
       <c r="G18" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="60">
@@ -2109,22 +2096,22 @@
         <v>56</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>198</v>
+        <v>172</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>196</v>
       </c>
       <c r="G19" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="60">
@@ -2135,22 +2122,22 @@
         <v>57</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>199</v>
+        <v>165</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>197</v>
       </c>
       <c r="G20" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="75">
@@ -2158,25 +2145,25 @@
         <v>52</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>200</v>
+        <v>166</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>198</v>
       </c>
       <c r="G21" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="60">
@@ -2187,25 +2174,25 @@
         <v>58</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>201</v>
+        <v>174</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>199</v>
       </c>
       <c r="G22" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="75">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="60">
       <c r="A23" s="10" t="s">
         <v>54</v>
       </c>
@@ -2213,22 +2200,22 @@
         <v>59</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>202</v>
+        <v>125</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="G23" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="75">
@@ -2236,441 +2223,441 @@
         <v>55</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>203</v>
+        <v>170</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="G24" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="75">
       <c r="A25" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>204</v>
+        <v>171</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>201</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>10</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="1" customFormat="1" ht="60">
       <c r="A26" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>66</v>
-      </c>
       <c r="C26" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>205</v>
+        <v>153</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>202</v>
       </c>
       <c r="G26" s="19" t="s">
         <v>19</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="1" customFormat="1" ht="60">
       <c r="A27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="C27" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>206</v>
+      <c r="F27" s="8" t="s">
+        <v>203</v>
       </c>
       <c r="G27" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="1" customFormat="1" ht="45">
       <c r="A28" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>207</v>
+        <v>74</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>204</v>
       </c>
       <c r="G28" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="45">
       <c r="A29" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>208</v>
+      <c r="F29" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="G29" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="90">
       <c r="A30" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B30" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" s="26" t="s">
-        <v>209</v>
+      <c r="F30" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="G30" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="75">
       <c r="A31" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="F31" s="26" t="s">
-        <v>210</v>
+        <v>168</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>207</v>
       </c>
       <c r="G31" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="105">
       <c r="A32" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="F32" s="26" t="s">
-        <v>211</v>
+        <v>81</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>208</v>
       </c>
       <c r="G32" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="105">
       <c r="A33" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>212</v>
+        <v>164</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>209</v>
       </c>
       <c r="G33" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="78" customHeight="1">
       <c r="A34" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="C34" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F34" s="26" t="s">
-        <v>213</v>
+      <c r="F34" s="8" t="s">
+        <v>210</v>
       </c>
       <c r="G34" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="84.75" customHeight="1">
       <c r="A35" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B35" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F35" s="26" t="s">
-        <v>214</v>
+      <c r="F35" s="8" t="s">
+        <v>211</v>
       </c>
       <c r="G35" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="75">
       <c r="A36" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="D36" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="E36" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="F36" s="26" t="s">
-        <v>215</v>
+      <c r="F36" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="G36" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="63.75" customHeight="1">
-      <c r="A37" s="40" t="s">
-        <v>165</v>
+      <c r="A37" s="34" t="s">
+        <v>163</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="60">
+      <c r="A38" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="B38" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="C38" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="E38" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="F38" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="60">
+      <c r="A39" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="45">
+      <c r="A40" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H37" s="39" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="60">
-      <c r="A38" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="B38" s="40" t="s">
-        <v>232</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="E38" s="41" t="s">
-        <v>247</v>
-      </c>
-      <c r="F38" s="41" t="s">
-        <v>234</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="60">
-      <c r="A39" s="40" t="s">
-        <v>235</v>
-      </c>
-      <c r="B39" s="41" t="s">
-        <v>236</v>
-      </c>
-      <c r="C39" s="8" t="s">
+      <c r="E40" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="D39" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="E39" s="8" t="s">
+      <c r="F40" s="35" t="s">
         <v>238</v>
       </c>
-      <c r="F39" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="45">
-      <c r="A40" s="40" t="s">
-        <v>239</v>
-      </c>
-      <c r="B40" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="C40" s="41" t="s">
-        <v>227</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="E40" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="F40" s="41" t="s">
-        <v>241</v>
-      </c>
       <c r="G40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2685,122 +2672,122 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
     <col min="3" max="3" width="54.85546875" customWidth="1"/>
-    <col min="4" max="4" width="40.5703125" customWidth="1"/>
-    <col min="5" max="5" width="41.140625" customWidth="1"/>
+    <col min="4" max="4" width="43.5703125" customWidth="1"/>
+    <col min="5" max="5" width="43.140625" customWidth="1"/>
     <col min="6" max="6" width="60.5703125" customWidth="1"/>
     <col min="7" max="7" width="51.7109375" customWidth="1"/>
-    <col min="8" max="8" width="30.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" customWidth="1"/>
     <col min="11" max="11" width="56.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="44" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60">
+      <c r="A2" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="60">
+      <c r="A3" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="32" t="s">
         <v>159</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="38" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="60">
-      <c r="A2" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F2" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="G2" s="45" t="s">
-        <v>217</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="60">
-      <c r="A3" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>220</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" s="34" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>
